--- a/resources/DatasetTemplate/subjects.xlsx
+++ b/resources/DatasetTemplate/subjects.xlsx
@@ -70,7 +70,7 @@
     <t xml:space="preserve">protocol title</t>
   </si>
   <si>
-    <t xml:space="preserve">protocol.io location</t>
+    <t xml:space="preserve">protocols.io location</t>
   </si>
   <si>
     <t xml:space="preserve">experimental log file name</t>

--- a/resources/DatasetTemplate/subjects.xlsx
+++ b/resources/DatasetTemplate/subjects.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">age range (min)</t>
   </si>
   <si>
-    <t xml:space="preserve">age range (max) disease</t>
+    <t xml:space="preserve">age range (max)</t>
   </si>
   <si>
     <t xml:space="preserve">handedness</t>
